--- a/output/PCB并购案例/PCB可比交易案例.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -558,12 +558,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>002134.SZ</t>
+          <t>002436.SZ</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>天津普林</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>泰和电路51%股权</t>
+          <t>揖斐电电子（北京）100%股权</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>印制电路板研发、生产、销售</t>
+          <t>PCB样板、小批量板、IC封装基板</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>印制电路板</t>
+          <t>HDI板、类载板</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -593,32 +593,34 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>100%现金（股权受让+增资）</t>
+          <t>100%现金</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>42310.3</v>
+        <v>87000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2022年12月31日</t>
+          <t>/</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>收益法</t>
+          <t>/</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>167.32%</t>
+          <t>/</t>
         </is>
       </c>
       <c r="M3" s="4" t="n">
-        <v>4176.94</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>12.84</v>
+        <v>-5464</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -634,12 +636,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>002436.SZ</t>
+          <t>688359.SH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>三孚新科</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -649,49 +651,49 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>揖斐电电子（北京）100%股权</t>
+          <t>明毅电子51%股权</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>PCB样板、小批量板、IC封装基板</t>
+          <t>PCB及表面处理专用化学品</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>HDI板、类载板</t>
+          <t>PCB及半导体电镀设备</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>横向整合</t>
+          <t>纵向整合</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>100%现金</t>
+          <t>100%现金（股权受让+增资）</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>87000</v>
+        <v>5000</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>2022年10月31日</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>资产基础法</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>270.43%</t>
         </is>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-5464</v>
+        <v>-373.19</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -712,50 +714,50 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>301362.SZ</t>
+          <t>002134.SZ</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>民爆光电</t>
+          <t>天津普林</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>51%已完成，49%审核中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>厦芝精密100%股权</t>
+          <t>泰和电路51%股权</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LED照明灯具</t>
+          <t>印制电路板研发、生产、销售</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>PCB微型钻针</t>
+          <t>印制电路板</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>跨界转型</t>
+          <t>横向整合</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>51%现金+49%发行股份</t>
+          <t>100%现金（股权受让+增资）</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>48000</v>
+        <v>42310.3</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2026年1月31日</t>
+          <t>2022年12月31日</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -765,136 +767,464 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>499.44%</t>
+          <t>167.32%</t>
         </is>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1068.69</v>
+        <v>4176.94</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>44.91</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>3700</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>12.97</v>
+        <v>12.84</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>688359.SH</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>三孚新科</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>江西博泉40.0788%股权</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>PCB及表面处理专用化学品</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>PCB专用电镀化学品</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>横向整合</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>100%现金</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>10019.7</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2023年4月30日</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>323.37%</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>1085.62</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>2660</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>300964.SZ</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>本川智能</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>珠海硕鸿100%股权</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>印制电路板研发、生产、销售</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>刚性板、刚柔结合板、柔性板</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>横向整合</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>100%现金</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>3950</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>637.3</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>301362.SZ</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>民爆光电</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>51%已完成，49%审核中</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>厦芝精密100%股权</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>LED照明灯具</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>PCB微型钻针</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>跨界转型</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>51%现金+49%发行股份</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>48000</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026年1月31日</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>499.44%</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>1068.69</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>3700</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>688308.SH</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>欧科亿</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>董事会通过，待股东会审议</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>永鑫精工51%股权</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>数控刀片、硬质合金棒材</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>PCB微钻、铣刀</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>纵向整合</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>100%现金（股权受让+增资）</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>42500</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>2026年3月31日</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>收益法</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>234.63%</t>
         </is>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>3310.85</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>21.14</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>7666.67</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>9.130000000000001</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>注1：天津普林交易作价含受让老股10,162.77万元及增资32,147.53万元；市盈率按100%股权评估值53,631.86万元计算，与重组报告书口径一致。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>注2：兴森科技定价为双方协商确定，未进行评估；交易作价为基础购买价格176.61亿日元（按20.3日元/元折算），最终价格按净资产变动调整；标的2021年亏损，市盈率不适用。</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>注3：民爆光电分两步实施，51%股权现金收购24,480万元、49%股权发行股份购买23,520万元，合并列示。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>注4：欧科亿交易作价含受让老股17,500万元及增资25,000万元；市盈率按增资投前估值70,000万元计算；评估增值率=评估值71,725.15万元÷2026年3月末净资产21,433.97万元−1。</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>688257.SH</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>新锐股份</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>董事会通过，待股东会审议</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>慧联电子80%股权</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>硬质合金、切削工具</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>PCB微钻、铣刀</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>纵向整合</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>100%现金</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026年5月31日</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>187.98%</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>3383.05</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>注1：兴森科技定价为双方协商确定，未进行评估；交易作价为基础购买价格176.61亿日元（按20.3日元/元折算），最终价格按净资产变动调整；标的2021年亏损，市盈率不适用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>注2：三孚新科收购明毅电子，以1元受让16.04%股权并增资5,000万元，合计持股51%；标的2021年亏损，市盈率不适用；无业绩承诺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>注3：天津普林交易作价含受让老股10,162.77万元及增资32,147.53万元；市盈率按100%股权评估值53,631.86万元计算，与重组报告书口径一致；无业绩承诺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>注4：三孚新科收购江西博泉前已持股10.9212%，交易后合计持股51%；市盈率按整体估值25,000万元计算；承诺2023–2025年净利润2,000/2,600/3,380万元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>注5：本川智能定价为双方协商确定，未进行评估；卖方为东山精密控制的硕鸿电路版（集团）；净利润为2023年数，无业绩承诺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>注6：民爆光电分两步实施，51%股权现金收购24,480万元、49%股权发行股份购买23,520万元，合并列示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>注7：欧科亿交易作价含受让老股17,500万元及增资25,000万元；市盈率按增资投前估值70,000万元计算；评估增值率=评估值71,725.15万元÷2026年3月末净资产21,433.97万元−1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>注8：新锐股份交易作价80,000万元为上限（基础价格56,000万元，最终按业绩承诺期累计扣非净利润÷3×12.5×80%确定）；市盈率按协商整体估值100,000万元计算；评估增值率=评估值100,800万元÷2026年5月末净资产35,002.92万元−1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>资料来源：各公司公告</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="A10:P10"/>
-    <mergeCell ref="A9:P9"/>
-    <mergeCell ref="A8:P8"/>
+  <mergeCells count="9">
+    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="A14:P14"/>
+    <mergeCell ref="A17:P17"/>
+    <mergeCell ref="A18:P18"/>
     <mergeCell ref="A12:P12"/>
+    <mergeCell ref="A20:P20"/>
+    <mergeCell ref="A16:P16"/>
+    <mergeCell ref="A15:P15"/>
+    <mergeCell ref="A19:P19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/PCB并购案例/PCB可比交易案例.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>董事会通过，待股东会审议</t>
+          <t>股东会审议通过</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">

--- a/output/PCB并购案例/PCB可比交易案例.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>董事会通过，待股东会审议</t>
+          <t>股东会审议通过</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">

--- a/output/PCB并购案例/PCB可比交易案例.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>股东会审议通过</t>
+          <t>已并表，工商变更办理中</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
